--- a/public/salehop-listing-import-template.xlsx
+++ b/public/salehop-listing-import-template.xlsx
@@ -1199,7 +1199,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>- One import handles up to 150 rows at a time. A bigger file can be split across a couple of uploads.</t>
+          <t>- One import handles up to 100 rows at a time. A bigger file can be split across a couple of uploads.</t>
         </is>
       </c>
     </row>
